--- a/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\startcamp\vibecoding\team_pjt\day03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D2F950-ADFD-40A1-8B75-B27F9CE97571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A301FF35-7853-4AF6-94F5-FBDA52B0804B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="293">
   <si>
     <t>실습 소재</t>
   </si>
@@ -19904,6 +19904,582 @@
         <b/>
         <sz val="10"/>
         <color rgb="FFFF0000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>선택</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소셜</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공유</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게시글</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>또는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추천</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> URL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주소를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클립보드에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+• navigator.clipboard.writeText</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버튼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>간단한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Toast </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알림을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>띄워</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>피드백</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
@@ -25788,9 +26364,6 @@
       <t>구체화</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>팀전체</t>
   </si>
   <si>
     <t>팀전체</t>
@@ -26862,136 +27435,6 @@
         <charset val="129"/>
       </rPr>
       <t>기재</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WBS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>실제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>진행</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최종</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>현행화</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정리</t>
     </r>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
@@ -27139,473 +27582,451 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>예정</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">UI/UX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>디자인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설계</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[Must] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서울</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공공데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(JSON) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파싱</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Netlify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>초기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빌드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로덕션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빌드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Netlify </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>호스팅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시연</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">WBS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최종</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>현행화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
     <t>완료</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">UI/UX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>디자인 설계</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[Must] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>서울</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>공공데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(JSON) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>파싱</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Netlify </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>초기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빌드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최종</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>프로덕션</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>빌드</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Netlify </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>호스팅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>완료</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>통합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시연</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>통합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>시연</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>테스트</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>컴포넌트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>구조도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>설계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로컬스토리지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>스키마</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작성</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -27979,13 +28400,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF222222"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF222222"/>
       <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
@@ -27996,6 +28410,14 @@
       <color rgb="FF222222"/>
       <name val="돋움"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
@@ -28015,7 +28437,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -28112,12 +28534,6 @@
         <bgColor rgb="FF222222"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -28201,7 +28617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -28277,6 +28693,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -28298,24 +28715,8 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -28351,6 +28752,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -28360,13 +28767,7 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -28384,15 +28785,6 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -28405,29 +28797,20 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -28465,39 +28848,35 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF028090"/>
-          <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF028090"/>
-          <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF028090"/>
-          <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -28824,10 +29203,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="42"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -28862,10 +29241,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="44"/>
+      <c r="C9" s="39"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -28916,28 +29295,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="46"/>
+      <c r="C17" s="41"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="49"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="42"/>
+      <c r="C19" s="37"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="42"/>
+      <c r="C20" s="37"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -28971,13 +29350,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -29069,46 +29448,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="44"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="39"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -29141,22 +29520,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="44"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="39"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -29185,504 +29564,522 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="28" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="27"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="28"/>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="27" t="s">
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="27" t="s">
+      <c r="E8" s="51"/>
+      <c r="F8" s="28" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="30" customHeight="1">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="28" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="28" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="27"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="28"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="27" t="s">
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="60"/>
-      <c r="F12" s="27" t="s">
+      <c r="E12" s="51"/>
+      <c r="F12" s="28" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="28" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="27"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="27" t="s">
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="E15" s="60"/>
-      <c r="F15" s="27" t="s">
+      <c r="E15" s="51"/>
+      <c r="F15" s="28" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="27"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="28"/>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="27" t="s">
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="60"/>
-      <c r="F17" s="27"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="60" t="s">
+      <c r="E18" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="60" t="s">
+      <c r="F18" s="51" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="27" t="s">
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="28" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="60" t="s">
+      <c r="E22" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="28" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="27"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="28"/>
     </row>
     <row r="24" spans="2:6" ht="30">
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="27" t="s">
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="60"/>
-      <c r="F24" s="27" t="s">
+      <c r="E24" s="51"/>
+      <c r="F24" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="27"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26" spans="2:6" ht="30">
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="27" t="s">
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="60"/>
-      <c r="F26" s="27" t="s">
+      <c r="E26" s="51"/>
+      <c r="F26" s="28" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="27"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="28"/>
     </row>
     <row r="28" spans="2:6" ht="30">
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="27" t="s">
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="60"/>
-      <c r="F28" s="27"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" spans="2:6" ht="60">
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="50" t="s">
         <v>193</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="60" t="s">
+      <c r="E29" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="28" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="27"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" spans="2:6" ht="60">
-      <c r="B31" s="58"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="27" t="s">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="60"/>
-      <c r="F31" s="27" t="s">
+      <c r="E31" s="51"/>
+      <c r="F31" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="27"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="28"/>
     </row>
     <row r="33" spans="2:6" ht="30">
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="27" t="s">
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="60"/>
-      <c r="F33" s="27"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="28"/>
     </row>
     <row r="34" spans="2:6" ht="30">
-      <c r="B34" s="58" t="s">
+      <c r="B34" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E34" s="60" t="s">
+      <c r="E34" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="28" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="27"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="28"/>
     </row>
     <row r="36" spans="2:6" ht="60">
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="27" t="s">
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="60"/>
-      <c r="F36" s="27" t="s">
+      <c r="E36" s="51"/>
+      <c r="F36" s="28" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="45">
-      <c r="B37" s="58" t="s">
+      <c r="B37" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="50" t="s">
         <v>207</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="28" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="27"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="28"/>
     </row>
     <row r="39" spans="2:6" ht="45">
-      <c r="B39" s="58"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="27" t="s">
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="60"/>
-      <c r="F39" s="27" t="s">
+      <c r="E39" s="51"/>
+      <c r="F39" s="28" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="45">
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="E40" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F40" s="27" t="s">
+      <c r="F40" s="28" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="41" spans="2:6" ht="60">
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F41" s="27" t="s">
+      <c r="F41" s="28" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="45">
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="E42" s="27" t="s">
+      <c r="E42" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F42" s="27" t="s">
+      <c r="F42" s="28" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="45">
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="C43" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E43" s="27" t="s">
+      <c r="E43" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F43" s="27" t="s">
+      <c r="F43" s="28" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="45">
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="D44" s="27" t="s">
+      <c r="D44" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="E44" s="27" t="s">
+      <c r="E44" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F44" s="27" t="s">
+      <c r="F44" s="28" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="60">
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D45" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="E45" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="F45" s="28" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="45">
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="E46" s="27" t="s">
+      <c r="E46" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="27" t="s">
+      <c r="F46" s="28" t="s">
         <v>233</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="E22:E28"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="E37:E39"/>
@@ -29692,24 +30089,6 @@
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="E34:E36"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="B22:B28"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="E22:E28"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -29734,37 +30113,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="44"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="44"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -29790,10 +30169,10 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="94.5">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="31" t="s">
         <v>242</v>
       </c>
       <c r="D6" s="5">
@@ -29812,7 +30191,7 @@
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="2:8" ht="94.5">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="30" t="s">
         <v>235</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -29836,7 +30215,7 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="94.5">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="30" t="s">
         <v>236</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -29858,10 +30237,10 @@
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="2:8" ht="81">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="32" t="s">
         <v>245</v>
       </c>
       <c r="D9" s="5">
@@ -29880,10 +30259,10 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="2:8" ht="94.5">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="32" t="s">
         <v>246</v>
       </c>
       <c r="D10" s="5">
@@ -29902,7 +30281,7 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11" spans="2:8" ht="94.5">
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="30" t="s">
         <v>239</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -29924,7 +30303,7 @@
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="2:8" ht="93.75">
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="30" t="s">
         <v>240</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -29946,10 +30325,10 @@
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="2:8" ht="94.5">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="32" t="s">
         <v>249</v>
       </c>
       <c r="D13" s="5">
@@ -29971,14 +30350,14 @@
       <c r="B15" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="63" t="s">
-        <v>264</v>
-      </c>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="46"/>
+      <c r="C15" s="58" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -29989,7 +30368,7 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="G6:G13">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>AND(G6&lt;&gt;"",G6&gt;=32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30013,7 +30392,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B2:M26"/>
+  <dimension ref="B2:C26"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -30022,19 +30401,19 @@
     <col min="4" max="4" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="30" customHeight="1">
-      <c r="B2" s="55" t="s">
+    <row r="2" spans="2:3" ht="30" customHeight="1">
+      <c r="B2" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="53"/>
+      <c r="C2" s="48"/>
     </row>
-    <row r="3" spans="2:4" ht="18" customHeight="1">
+    <row r="3" spans="2:3" ht="18" customHeight="1">
       <c r="B3" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="44"/>
+      <c r="C3" s="39"/>
     </row>
-    <row r="4" spans="2:4" ht="30" customHeight="1">
+    <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>44</v>
       </c>
@@ -30042,153 +30421,135 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="103.5" customHeight="1">
+    <row r="5" spans="2:3" ht="103.5" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>265</v>
+      <c r="C5" s="32" t="s">
+        <v>266</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="96.75" customHeight="1">
+    <row r="6" spans="2:3" ht="96.75" customHeight="1">
       <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="213" customHeight="1">
+    <row r="7" spans="2:3" ht="213" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="D7" s="94" t="s">
-        <v>295</v>
+      <c r="C7" s="32" t="s">
+        <v>268</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="15" customHeight="1">
+    <row r="9" spans="2:3" ht="15" customHeight="1">
       <c r="B9" s="66" t="s">
         <v>48</v>
       </c>
       <c r="C9" s="67"/>
     </row>
-    <row r="10" spans="2:4" ht="88.5" customHeight="1">
-      <c r="B10" s="48" t="s">
+    <row r="10" spans="2:3" ht="88.5" customHeight="1">
+      <c r="B10" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="C10" s="49"/>
+      <c r="C10" s="44"/>
     </row>
-    <row r="11" spans="2:4" ht="73.5" customHeight="1">
-      <c r="B11" s="65" t="s">
+    <row r="11" spans="2:3" ht="73.5" customHeight="1">
+      <c r="B11" s="60" t="s">
         <v>253</v>
       </c>
-      <c r="C11" s="49"/>
+      <c r="C11" s="44"/>
     </row>
-    <row r="12" spans="2:4" ht="118.5" customHeight="1">
-      <c r="B12" s="65" t="s">
+    <row r="12" spans="2:3" ht="118.5" customHeight="1">
+      <c r="B12" s="60" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="49"/>
+      <c r="C12" s="44"/>
     </row>
-    <row r="13" spans="2:4" ht="116.25" customHeight="1">
-      <c r="B13" s="48" t="s">
+    <row r="13" spans="2:3" ht="116.25" customHeight="1">
+      <c r="B13" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="49"/>
+      <c r="C13" s="44"/>
     </row>
-    <row r="14" spans="2:4" ht="63" customHeight="1">
-      <c r="B14" s="48" t="s">
+    <row r="14" spans="2:3" ht="63" customHeight="1">
+      <c r="B14" s="43" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="44"/>
     </row>
-    <row r="16" spans="2:4" ht="15" customHeight="1">
-      <c r="B16" s="71" t="s">
+    <row r="16" spans="2:3" ht="15" customHeight="1">
+      <c r="B16" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="72"/>
+      <c r="C16" s="64"/>
     </row>
-    <row r="17" spans="2:13" ht="89.25" customHeight="1">
-      <c r="B17" s="48" t="s">
+    <row r="17" spans="2:3" ht="89.25" customHeight="1">
+      <c r="B17" s="43" t="s">
         <v>257</v>
       </c>
-      <c r="C17" s="49"/>
+      <c r="C17" s="44"/>
     </row>
-    <row r="18" spans="2:13" ht="85.5" customHeight="1">
-      <c r="B18" s="65" t="s">
+    <row r="18" spans="2:3" ht="85.5" customHeight="1">
+      <c r="B18" s="60" t="s">
         <v>258</v>
       </c>
-      <c r="C18" s="49"/>
+      <c r="C18" s="44"/>
     </row>
-    <row r="19" spans="2:13" ht="30" customHeight="1">
-      <c r="B19" s="65" t="s">
+    <row r="19" spans="2:3" ht="99.75" customHeight="1">
+      <c r="B19" s="60" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="94" t="s">
-        <v>294</v>
-      </c>
+      <c r="C19" s="44"/>
     </row>
-    <row r="20" spans="2:13" ht="70.5" customHeight="1">
-      <c r="B20" s="38" t="s">
+    <row r="20" spans="2:3" ht="70.5" customHeight="1">
+      <c r="B20" s="65" t="s">
         <v>263</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
+      <c r="C20" s="44"/>
     </row>
-    <row r="21" spans="2:13" ht="73.5" customHeight="1">
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
+    <row r="21" spans="2:3" ht="73.5" customHeight="1">
+      <c r="B21" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" s="44"/>
     </row>
-    <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="69" t="s">
+    <row r="22" spans="2:3" ht="15" customHeight="1"/>
+    <row r="23" spans="2:3" ht="15" customHeight="1">
+      <c r="B23" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="70"/>
+      <c r="C23" s="62"/>
     </row>
-    <row r="23" spans="2:13" ht="15" customHeight="1"/>
-    <row r="24" spans="2:13" ht="77.25" customHeight="1">
-      <c r="B24" s="65" t="s">
+    <row r="24" spans="2:3" ht="77.25" customHeight="1">
+      <c r="B24" s="60" t="s">
         <v>260</v>
       </c>
-      <c r="C24" s="49"/>
+      <c r="C24" s="44"/>
     </row>
-    <row r="25" spans="2:13" ht="55.5" customHeight="1">
-      <c r="B25" s="48" t="s">
+    <row r="25" spans="2:3" ht="55.5" customHeight="1">
+      <c r="B25" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="C25" s="49"/>
+      <c r="C25" s="44"/>
     </row>
-    <row r="26" spans="2:13" ht="56.25" customHeight="1">
-      <c r="B26" s="65" t="s">
+    <row r="26" spans="2:3" ht="56.25" customHeight="1">
+      <c r="B26" s="60" t="s">
         <v>262</v>
       </c>
-      <c r="C26" s="49"/>
+      <c r="C26" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B24:C24"/>
@@ -30197,14 +30558,10 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30234,36 +30591,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="44"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="39"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="12" t="s">
@@ -30311,15 +30668,15 @@
         <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E5" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <v>46217</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <v>46217</v>
       </c>
       <c r="H5" s="5">
@@ -30329,10 +30686,10 @@
       <c r="I5" s="5">
         <v>100</v>
       </c>
-      <c r="J5" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="K5" s="39"/>
+      <c r="J5" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
@@ -30344,12 +30701,12 @@
         <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E6" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="34">
         <v>46217</v>
       </c>
       <c r="G6" s="35">
@@ -30362,10 +30719,10 @@
       <c r="I6" s="5">
         <v>100</v>
       </c>
-      <c r="J6" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="K6" s="39"/>
+      <c r="J6" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -30376,16 +30733,16 @@
       <c r="C7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="32" t="s">
         <v>272</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="F7" s="33">
+        <v>282</v>
+      </c>
+      <c r="F7" s="34">
         <v>46217</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="34">
         <v>46217</v>
       </c>
       <c r="H7" s="5">
@@ -30395,10 +30752,8 @@
       <c r="I7" s="5">
         <v>0</v>
       </c>
-      <c r="J7" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="K7" s="39"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -30410,12 +30765,12 @@
         <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F8" s="33">
+        <v>283</v>
+      </c>
+      <c r="F8" s="34">
         <v>46217</v>
       </c>
       <c r="G8" s="35">
@@ -30428,10 +30783,8 @@
       <c r="I8" s="5">
         <v>0</v>
       </c>
-      <c r="J8" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="K8" s="39"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
@@ -30446,12 +30799,12 @@
         <v>273</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F9" s="33">
+        <v>284</v>
+      </c>
+      <c r="F9" s="34">
         <v>46217</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="34">
         <v>46217</v>
       </c>
       <c r="H9" s="5">
@@ -30461,10 +30814,8 @@
       <c r="I9" s="5">
         <v>0</v>
       </c>
-      <c r="J9" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="K9" s="39"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
@@ -30476,15 +30827,15 @@
         <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F10" s="33">
+        <v>283</v>
+      </c>
+      <c r="F10" s="34">
         <v>46217</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="34">
         <v>46218</v>
       </c>
       <c r="H10" s="5">
@@ -30494,11 +30845,9 @@
       <c r="I10" s="5">
         <v>0</v>
       </c>
-      <c r="J10" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="2:13" ht="30" customHeight="1">
@@ -30512,12 +30861,12 @@
         <v>274</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F11" s="33">
+        <v>284</v>
+      </c>
+      <c r="F11" s="34">
         <v>46217</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="34">
         <v>46218</v>
       </c>
       <c r="H11" s="5">
@@ -30527,11 +30876,9 @@
       <c r="I11" s="5">
         <v>0</v>
       </c>
-      <c r="J11" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:13" ht="30" customHeight="1">
@@ -30545,12 +30892,12 @@
         <v>275</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F12" s="33">
+        <v>285</v>
+      </c>
+      <c r="F12" s="34">
         <v>46217</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="34">
         <v>46218</v>
       </c>
       <c r="H12" s="5">
@@ -30560,11 +30907,9 @@
       <c r="I12" s="5">
         <v>0</v>
       </c>
-      <c r="J12" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
@@ -30578,12 +30923,12 @@
         <v>276</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F13" s="33">
+        <v>283</v>
+      </c>
+      <c r="F13" s="34">
         <v>46218</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="34">
         <v>46218</v>
       </c>
       <c r="H13" s="5">
@@ -30593,14 +30938,12 @@
       <c r="I13" s="5">
         <v>0</v>
       </c>
-      <c r="J13" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J13" s="5"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="39"/>
+      <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="2:13" ht="37.5">
+    <row r="14" spans="2:13" ht="30" customHeight="1">
       <c r="B14" s="5">
         <v>10</v>
       </c>
@@ -30611,12 +30954,12 @@
         <v>277</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F14" s="33">
+        <v>284</v>
+      </c>
+      <c r="F14" s="34">
         <v>46218</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="34">
         <v>46218</v>
       </c>
       <c r="H14" s="5">
@@ -30626,11 +30969,9 @@
       <c r="I14" s="5">
         <v>0</v>
       </c>
-      <c r="J14" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J14" s="5"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="39"/>
+      <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:13" ht="30" customHeight="1">
@@ -30644,12 +30985,12 @@
         <v>278</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F15" s="33">
+        <v>285</v>
+      </c>
+      <c r="F15" s="34">
         <v>46218</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="34">
         <v>46218</v>
       </c>
       <c r="H15" s="5">
@@ -30659,11 +31000,9 @@
       <c r="I15" s="5">
         <v>0</v>
       </c>
-      <c r="J15" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J15" s="5"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="39"/>
+      <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="2:13" ht="30" customHeight="1">
@@ -30677,12 +31016,12 @@
         <v>279</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F16" s="33">
+        <v>285</v>
+      </c>
+      <c r="F16" s="34">
         <v>46218</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="34">
         <v>46219</v>
       </c>
       <c r="H16" s="5">
@@ -30692,12 +31031,10 @@
       <c r="I16" s="5">
         <v>0</v>
       </c>
-      <c r="J16" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J16" s="5"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
     </row>
     <row r="17" spans="2:16" ht="30" customHeight="1">
       <c r="B17" s="5">
@@ -30707,15 +31044,15 @@
         <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F17" s="33">
+        <v>284</v>
+      </c>
+      <c r="F17" s="34">
         <v>46217</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="34">
         <v>46217</v>
       </c>
       <c r="H17" s="5">
@@ -30725,10 +31062,8 @@
       <c r="I17" s="5">
         <v>0</v>
       </c>
-      <c r="J17" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="K17" s="39"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
@@ -30739,16 +31074,16 @@
       <c r="C18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>292</v>
+      <c r="D18" s="32" t="s">
+        <v>289</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F18" s="33">
+        <v>284</v>
+      </c>
+      <c r="F18" s="34">
         <v>46219</v>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="34">
         <v>46219</v>
       </c>
       <c r="H18" s="5">
@@ -30758,12 +31093,10 @@
       <c r="I18" s="5">
         <v>0</v>
       </c>
-      <c r="J18" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J18" s="5"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="39"/>
+      <c r="M18" s="3"/>
     </row>
     <row r="19" spans="2:16" ht="30" customHeight="1">
       <c r="B19" s="5">
@@ -30772,213 +31105,228 @@
       <c r="C19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="E19" s="32" t="s">
+      <c r="D19" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="34">
         <v>46219</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="34">
         <v>46219</v>
       </c>
       <c r="H19" s="5">
-        <f t="shared" ref="H19" si="1">IF(OR(F19="",G19=""),"",G19-F19+1)</f>
+        <f t="shared" ref="H19:H21" si="1">IF(OR(F19="",G19=""),"",G19-F19+1)</f>
         <v>1</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
       </c>
-      <c r="J19" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J19" s="5"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="39"/>
+      <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="2:16" ht="25.5">
+    <row r="20" spans="2:16" ht="30" customHeight="1">
       <c r="B20" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="32" t="s">
         <v>280</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F20" s="33">
+        <v>283</v>
+      </c>
+      <c r="F20" s="34">
         <v>46218</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="34">
         <v>46219</v>
       </c>
       <c r="H20" s="5">
-        <f>IF(OR(F20="",G20=""),"",G20-F20+1)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
       </c>
-      <c r="J20" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J20" s="5"/>
       <c r="K20" s="3"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="O20" s="75" t="s">
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="O20" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="P20" s="76"/>
+      <c r="P20" s="85"/>
     </row>
     <row r="21" spans="2:16" ht="30" customHeight="1">
       <c r="B21" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>281</v>
+      <c r="D21" s="32" t="s">
+        <v>291</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F21" s="33">
+        <v>284</v>
+      </c>
+      <c r="F21" s="34">
         <v>46219</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <v>46219</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" ref="H21:H22" si="2">IF(OR(F21="",G21=""),"",G21-F21+1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
       </c>
-      <c r="J21" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J21" s="5"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="39"/>
-      <c r="O21" s="77" t="s">
+      <c r="M21" s="3"/>
+      <c r="O21" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="P21" s="78"/>
+      <c r="P21" s="87"/>
     </row>
     <row r="22" spans="2:16" ht="30" customHeight="1">
       <c r="B22" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>270</v>
-      </c>
-      <c r="F22" s="33">
+      <c r="D22" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" s="34">
         <v>46218</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <v>46219</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H22:H23" si="2">IF(OR(F22="",G22=""),"",G22-F22+1)</f>
         <v>2</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
-      <c r="J22" s="40" t="s">
-        <v>287</v>
-      </c>
+      <c r="J22" s="5"/>
       <c r="K22" s="3"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="O22" s="79" t="s">
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="O22" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="P22" s="80"/>
+      <c r="P22" s="89"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
-      <c r="O23" s="83" t="s">
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="O23" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="84"/>
+      <c r="P23" s="73"/>
     </row>
     <row r="24" spans="2:16" ht="15" customHeight="1">
-      <c r="O24" s="85" t="s">
+      <c r="O24" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="P24" s="86"/>
+      <c r="P24" s="75"/>
     </row>
     <row r="25" spans="2:16" ht="15" customHeight="1">
-      <c r="O25" s="87" t="s">
+      <c r="O25" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="P25" s="88"/>
+      <c r="P25" s="77"/>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1">
-      <c r="O26" s="89" t="s">
+      <c r="O26" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="90"/>
+      <c r="P26" s="79"/>
     </row>
     <row r="27" spans="2:16" ht="15" customHeight="1">
-      <c r="O27" s="91" t="s">
+      <c r="O27" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="92"/>
+      <c r="P27" s="81"/>
     </row>
     <row r="28" spans="2:16" ht="15" customHeight="1">
-      <c r="O28" s="81" t="s">
+      <c r="O28" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="P28" s="82"/>
+      <c r="P28" s="71"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="93"/>
-      <c r="C29" s="93"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="93"/>
-      <c r="C30" s="93"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="93"/>
-      <c r="C32" s="93"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="93"/>
-      <c r="C33" s="93"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="93"/>
-      <c r="C34" s="93"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="93"/>
-      <c r="C35" s="93"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="93"/>
-      <c r="C36" s="93"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -30987,62 +31335,31 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
-  <conditionalFormatting sqref="K5:M5 K18:L18 L6:M9 M10:M15 K13:K16 L17:M17 K20:M22">
-    <cfRule type="expression" dxfId="8" priority="18">
+  <conditionalFormatting sqref="K5:M18">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K19:L19">
-    <cfRule type="expression" dxfId="7" priority="16">
+  <conditionalFormatting sqref="K19:M19">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>AND(K$4&gt;=$F19,K$4&lt;=$G19)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="expression" dxfId="6" priority="11">
-      <formula>AND(K$4&gt;=$F6,K$4&lt;=$G6)</formula>
+  <conditionalFormatting sqref="K20:M20">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>AND(K$4&gt;=$F20,K$4&lt;=$G20)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K12">
-    <cfRule type="expression" dxfId="5" priority="10">
-      <formula>AND(K$4&gt;=$F7,K$4&lt;=$G7)</formula>
+  <conditionalFormatting sqref="K22:M22">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>AND(K$4&gt;=$F22,K$4&lt;=$G22)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10:L15">
-    <cfRule type="expression" dxfId="4" priority="9">
-      <formula>AND(L$4&gt;=$F10,L$4&lt;=$G10)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L16:M16">
-    <cfRule type="expression" dxfId="3" priority="8">
-      <formula>AND(L$4&gt;=$F16,L$4&lt;=$G16)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K17">
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>AND(K$4&gt;=$F17,K$4&lt;=$G17)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M18">
-    <cfRule type="expression" dxfId="1" priority="6">
-      <formula>AND(M$4&gt;=$F18,M$4&lt;=$G18)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M19">
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>AND(M$4&gt;=$F19,M$4&lt;=$G19)</formula>
+  <conditionalFormatting sqref="K21:M21">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(K$4&gt;=$F21,K$4&lt;=$G21)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -31074,16 +31391,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="53"/>
+      <c r="C2" s="48"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="44"/>
+      <c r="C3" s="39"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">

--- a/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\팀 프로젝트\localhub\localhub\day03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A301FF35-7853-4AF6-94F5-FBDA52B0804B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05A913A-FEE0-4411-8702-FAF4F12C67D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="1425" windowWidth="18195" windowHeight="18690" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="295">
   <si>
     <t>실습 소재</t>
   </si>
@@ -28027,6 +28027,14 @@
   </si>
   <si>
     <t>완료</t>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">완료 </t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -28752,12 +28760,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -28767,7 +28769,13 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -28785,6 +28793,15 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -28800,17 +28817,29 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -28848,43 +28877,14 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF028090"/>
-          <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -29520,7 +29520,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="48"/>
@@ -29529,7 +29529,7 @@
       <c r="F2" s="48"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="51" t="s">
         <v>140</v>
       </c>
       <c r="C3" s="46"/>
@@ -29564,16 +29564,16 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="52" t="s">
         <v>151</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="54" t="s">
         <v>154</v>
       </c>
       <c r="F6" s="28" t="s">
@@ -29581,19 +29581,19 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="51"/>
+      <c r="E7" s="55"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="51"/>
+      <c r="E8" s="55"/>
       <c r="F8" s="28" t="s">
         <v>156</v>
       </c>
@@ -29616,16 +29616,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="53" t="s">
         <v>161</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="55" t="s">
         <v>164</v>
       </c>
       <c r="F10" s="28" t="s">
@@ -29633,34 +29633,34 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="28"/>
-      <c r="E11" s="51"/>
+      <c r="E11" s="55"/>
       <c r="F11" s="28"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="51"/>
+      <c r="E12" s="55"/>
       <c r="F12" s="28" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="53" t="s">
         <v>167</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="55" t="s">
         <v>171</v>
       </c>
       <c r="F13" s="28" t="s">
@@ -29668,71 +29668,71 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="28"/>
-      <c r="E14" s="51"/>
+      <c r="E14" s="55"/>
       <c r="F14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="E15" s="51"/>
+      <c r="E15" s="55"/>
       <c r="F15" s="28" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="28"/>
-      <c r="E16" s="51"/>
+      <c r="E16" s="55"/>
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
       <c r="D17" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="51"/>
+      <c r="E17" s="55"/>
       <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="53" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="55" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
       <c r="B21" s="29" t="s">
@@ -29752,16 +29752,16 @@
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="53" t="s">
         <v>184</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="55" t="s">
         <v>189</v>
       </c>
       <c r="F22" s="28" t="s">
@@ -29769,68 +29769,68 @@
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="51"/>
+      <c r="E23" s="55"/>
       <c r="F23" s="28"/>
     </row>
     <row r="24" spans="2:6" ht="30">
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
       <c r="D24" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="51"/>
+      <c r="E24" s="55"/>
       <c r="F24" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="28"/>
-      <c r="E25" s="51"/>
+      <c r="E25" s="55"/>
       <c r="F25" s="28"/>
     </row>
     <row r="26" spans="2:6" ht="30">
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
       <c r="D26" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="51"/>
+      <c r="E26" s="55"/>
       <c r="F26" s="28" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="51"/>
+      <c r="E27" s="55"/>
       <c r="F27" s="28"/>
     </row>
     <row r="28" spans="2:6" ht="30">
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
       <c r="D28" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="51"/>
+      <c r="E28" s="55"/>
       <c r="F28" s="28"/>
     </row>
     <row r="29" spans="2:6" ht="60">
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="53" t="s">
         <v>193</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="55" t="s">
         <v>197</v>
       </c>
       <c r="F29" s="28" t="s">
@@ -29838,50 +29838,50 @@
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="51"/>
+      <c r="E30" s="55"/>
       <c r="F30" s="28"/>
     </row>
     <row r="31" spans="2:6" ht="60">
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
       <c r="D31" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="51"/>
+      <c r="E31" s="55"/>
       <c r="F31" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
       <c r="D32" s="28"/>
-      <c r="E32" s="51"/>
+      <c r="E32" s="55"/>
       <c r="F32" s="28"/>
     </row>
     <row r="33" spans="2:6" ht="30">
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
       <c r="D33" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="51"/>
+      <c r="E33" s="55"/>
       <c r="F33" s="28"/>
     </row>
     <row r="34" spans="2:6" ht="30">
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="53" t="s">
         <v>200</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="55" t="s">
         <v>203</v>
       </c>
       <c r="F34" s="28" t="s">
@@ -29889,34 +29889,34 @@
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="51"/>
+      <c r="E35" s="55"/>
       <c r="F35" s="28"/>
     </row>
     <row r="36" spans="2:6" ht="60">
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
       <c r="D36" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="51"/>
+      <c r="E36" s="55"/>
       <c r="F36" s="28" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="45">
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="53" t="s">
         <v>207</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="51" t="s">
+      <c r="E37" s="55" t="s">
         <v>210</v>
       </c>
       <c r="F37" s="28" t="s">
@@ -29924,19 +29924,19 @@
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
       <c r="D38" s="28"/>
-      <c r="E38" s="51"/>
+      <c r="E38" s="55"/>
       <c r="F38" s="28"/>
     </row>
     <row r="39" spans="2:6" ht="45">
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
       <c r="D39" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="51"/>
+      <c r="E39" s="55"/>
       <c r="F39" s="28" t="s">
         <v>212</v>
       </c>
@@ -30062,24 +30062,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="B22:B28"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="E22:E28"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="E37:E39"/>
@@ -30089,10 +30071,28 @@
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="E34:E36"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="E22:E28"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30368,7 +30368,7 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="G6:G13">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>AND(G6&lt;&gt;"",G6&gt;=32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30402,13 +30402,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="48"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="63" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="39"/>
@@ -30446,10 +30446,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="67"/>
+      <c r="C9" s="62"/>
     </row>
     <row r="10" spans="2:3" ht="88.5" customHeight="1">
       <c r="B10" s="43" t="s">
@@ -30482,10 +30482,10 @@
       <c r="C14" s="44"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="64"/>
+      <c r="C16" s="67"/>
     </row>
     <row r="17" spans="2:3" ht="89.25" customHeight="1">
       <c r="B17" s="43" t="s">
@@ -30506,23 +30506,23 @@
       <c r="C19" s="44"/>
     </row>
     <row r="20" spans="2:3" ht="70.5" customHeight="1">
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="68" t="s">
         <v>263</v>
       </c>
       <c r="C20" s="44"/>
     </row>
     <row r="21" spans="2:3" ht="73.5" customHeight="1">
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="68" t="s">
         <v>264</v>
       </c>
       <c r="C21" s="44"/>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1"/>
     <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="62"/>
+      <c r="C23" s="65"/>
     </row>
     <row r="24" spans="2:3" ht="77.25" customHeight="1">
       <c r="B24" s="60" t="s">
@@ -30544,12 +30544,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B24:C24"/>
@@ -30562,6 +30556,12 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30591,7 +30591,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="70" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="48"/>
@@ -30607,7 +30607,7 @@
       <c r="M2" s="48"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="69" t="s">
         <v>135</v>
       </c>
       <c r="C3" s="46"/>
@@ -30814,7 +30814,9 @@
       <c r="I9" s="5">
         <v>0</v>
       </c>
-      <c r="J9" s="5"/>
+      <c r="J9" s="33" t="s">
+        <v>294</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -30876,7 +30878,9 @@
       <c r="I11" s="5">
         <v>0</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="33" t="s">
+        <v>294</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -30969,7 +30973,9 @@
       <c r="I14" s="5">
         <v>0</v>
       </c>
-      <c r="J14" s="5"/>
+      <c r="J14" s="5" t="s">
+        <v>293</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -31159,10 +31165,10 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="O20" s="84" t="s">
+      <c r="O20" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="P20" s="85"/>
+      <c r="P20" s="72"/>
     </row>
     <row r="21" spans="2:16" ht="30" customHeight="1">
       <c r="B21" s="5">
@@ -31194,10 +31200,10 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="O21" s="86" t="s">
+      <c r="O21" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="P21" s="87"/>
+      <c r="P21" s="74"/>
     </row>
     <row r="22" spans="2:16" ht="30" customHeight="1">
       <c r="B22" s="5">
@@ -31219,7 +31225,7 @@
         <v>46219</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" ref="H22:H23" si="2">IF(OR(F22="",G22=""),"",G22-F22+1)</f>
+        <f t="shared" ref="H22" si="2">IF(OR(F22="",G22=""),"",G22-F22+1)</f>
         <v>2</v>
       </c>
       <c r="I22" s="5">
@@ -31229,10 +31235,10 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
-      <c r="O22" s="88" t="s">
+      <c r="O22" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="P22" s="89"/>
+      <c r="P22" s="76"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
       <c r="B23" s="27"/>
@@ -31247,86 +31253,75 @@
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
-      <c r="O23" s="72" t="s">
+      <c r="O23" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="73"/>
+      <c r="P23" s="80"/>
     </row>
     <row r="24" spans="2:16" ht="15" customHeight="1">
-      <c r="O24" s="74" t="s">
+      <c r="O24" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="P24" s="75"/>
+      <c r="P24" s="82"/>
     </row>
     <row r="25" spans="2:16" ht="15" customHeight="1">
-      <c r="O25" s="76" t="s">
+      <c r="O25" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="P25" s="77"/>
+      <c r="P25" s="84"/>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1">
-      <c r="O26" s="78" t="s">
+      <c r="O26" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="79"/>
+      <c r="P26" s="86"/>
     </row>
     <row r="27" spans="2:16" ht="15" customHeight="1">
-      <c r="O27" s="80" t="s">
+      <c r="O27" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="81"/>
+      <c r="P27" s="88"/>
     </row>
     <row r="28" spans="2:16" ht="15" customHeight="1">
-      <c r="O28" s="70" t="s">
+      <c r="O28" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="P28" s="71"/>
+      <c r="P28" s="78"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -31335,30 +31330,41 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:M19">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>AND(K$4&gt;=$F19,K$4&lt;=$G19)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K20:M20">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>AND(K$4&gt;=$F20,K$4&lt;=$G20)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AND(K$4&gt;=$F22,K$4&lt;=$G22)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:M21">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND(K$4&gt;=$F21,K$4&lt;=$G21)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vibecoding_team_pjt\day03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A301FF35-7853-4AF6-94F5-FBDA52B0804B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490F46F3-72C1-4CDC-95F2-DC37B8B450C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28752,12 +28752,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -28767,7 +28761,13 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -28785,6 +28785,15 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -28800,17 +28809,29 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -28848,43 +28869,14 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF028090"/>
-          <bgColor rgb="FF028090"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -29520,7 +29512,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="48"/>
@@ -29529,7 +29521,7 @@
       <c r="F2" s="48"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="51" t="s">
         <v>140</v>
       </c>
       <c r="C3" s="46"/>
@@ -29564,16 +29556,16 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="52" t="s">
         <v>151</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="54" t="s">
         <v>154</v>
       </c>
       <c r="F6" s="28" t="s">
@@ -29581,19 +29573,19 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="51"/>
+      <c r="E7" s="55"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="51"/>
+      <c r="E8" s="55"/>
       <c r="F8" s="28" t="s">
         <v>156</v>
       </c>
@@ -29616,16 +29608,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="53" t="s">
         <v>161</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="55" t="s">
         <v>164</v>
       </c>
       <c r="F10" s="28" t="s">
@@ -29633,34 +29625,34 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="28"/>
-      <c r="E11" s="51"/>
+      <c r="E11" s="55"/>
       <c r="F11" s="28"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="51"/>
+      <c r="E12" s="55"/>
       <c r="F12" s="28" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="53" t="s">
         <v>167</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="55" t="s">
         <v>171</v>
       </c>
       <c r="F13" s="28" t="s">
@@ -29668,71 +29660,71 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="28"/>
-      <c r="E14" s="51"/>
+      <c r="E14" s="55"/>
       <c r="F14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="E15" s="51"/>
+      <c r="E15" s="55"/>
       <c r="F15" s="28" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="28"/>
-      <c r="E16" s="51"/>
+      <c r="E16" s="55"/>
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
       <c r="D17" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="51"/>
+      <c r="E17" s="55"/>
       <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="53" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="53" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="55" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
       <c r="B21" s="29" t="s">
@@ -29752,16 +29744,16 @@
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="53" t="s">
         <v>184</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="55" t="s">
         <v>189</v>
       </c>
       <c r="F22" s="28" t="s">
@@ -29769,68 +29761,68 @@
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="51"/>
+      <c r="E23" s="55"/>
       <c r="F23" s="28"/>
     </row>
     <row r="24" spans="2:6" ht="30">
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
       <c r="D24" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="51"/>
+      <c r="E24" s="55"/>
       <c r="F24" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="28"/>
-      <c r="E25" s="51"/>
+      <c r="E25" s="55"/>
       <c r="F25" s="28"/>
     </row>
     <row r="26" spans="2:6" ht="30">
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
       <c r="D26" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="51"/>
+      <c r="E26" s="55"/>
       <c r="F26" s="28" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="51"/>
+      <c r="E27" s="55"/>
       <c r="F27" s="28"/>
     </row>
     <row r="28" spans="2:6" ht="30">
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
       <c r="D28" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="51"/>
+      <c r="E28" s="55"/>
       <c r="F28" s="28"/>
     </row>
     <row r="29" spans="2:6" ht="60">
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="53" t="s">
         <v>193</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="55" t="s">
         <v>197</v>
       </c>
       <c r="F29" s="28" t="s">
@@ -29838,50 +29830,50 @@
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="51"/>
+      <c r="E30" s="55"/>
       <c r="F30" s="28"/>
     </row>
     <row r="31" spans="2:6" ht="60">
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
       <c r="D31" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="51"/>
+      <c r="E31" s="55"/>
       <c r="F31" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
       <c r="D32" s="28"/>
-      <c r="E32" s="51"/>
+      <c r="E32" s="55"/>
       <c r="F32" s="28"/>
     </row>
     <row r="33" spans="2:6" ht="30">
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
       <c r="D33" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="51"/>
+      <c r="E33" s="55"/>
       <c r="F33" s="28"/>
     </row>
     <row r="34" spans="2:6" ht="30">
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="53" t="s">
         <v>200</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="55" t="s">
         <v>203</v>
       </c>
       <c r="F34" s="28" t="s">
@@ -29889,34 +29881,34 @@
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="51"/>
+      <c r="E35" s="55"/>
       <c r="F35" s="28"/>
     </row>
     <row r="36" spans="2:6" ht="60">
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
       <c r="D36" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="51"/>
+      <c r="E36" s="55"/>
       <c r="F36" s="28" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="45">
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="53" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="53" t="s">
         <v>207</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="51" t="s">
+      <c r="E37" s="55" t="s">
         <v>210</v>
       </c>
       <c r="F37" s="28" t="s">
@@ -29924,19 +29916,19 @@
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
       <c r="D38" s="28"/>
-      <c r="E38" s="51"/>
+      <c r="E38" s="55"/>
       <c r="F38" s="28"/>
     </row>
     <row r="39" spans="2:6" ht="45">
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
       <c r="D39" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="51"/>
+      <c r="E39" s="55"/>
       <c r="F39" s="28" t="s">
         <v>212</v>
       </c>
@@ -30062,24 +30054,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="B22:B28"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="E22:E28"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="E37:E39"/>
@@ -30089,6 +30063,24 @@
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="E34:E36"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="E22:E28"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30368,7 +30360,7 @@
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="G6:G13">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>AND(G6&lt;&gt;"",G6&gt;=32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30402,13 +30394,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="50" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="48"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="63" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="39"/>
@@ -30446,10 +30438,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="67"/>
+      <c r="C9" s="62"/>
     </row>
     <row r="10" spans="2:3" ht="88.5" customHeight="1">
       <c r="B10" s="43" t="s">
@@ -30482,10 +30474,10 @@
       <c r="C14" s="44"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="64"/>
+      <c r="C16" s="67"/>
     </row>
     <row r="17" spans="2:3" ht="89.25" customHeight="1">
       <c r="B17" s="43" t="s">
@@ -30506,23 +30498,23 @@
       <c r="C19" s="44"/>
     </row>
     <row r="20" spans="2:3" ht="70.5" customHeight="1">
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="68" t="s">
         <v>263</v>
       </c>
       <c r="C20" s="44"/>
     </row>
     <row r="21" spans="2:3" ht="73.5" customHeight="1">
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="68" t="s">
         <v>264</v>
       </c>
       <c r="C21" s="44"/>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1"/>
     <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="62"/>
+      <c r="C23" s="65"/>
     </row>
     <row r="24" spans="2:3" ht="77.25" customHeight="1">
       <c r="B24" s="60" t="s">
@@ -30544,12 +30536,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B24:C24"/>
@@ -30562,6 +30548,12 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30591,7 +30583,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="70" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="48"/>
@@ -30607,7 +30599,7 @@
       <c r="M2" s="48"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="69" t="s">
         <v>135</v>
       </c>
       <c r="C3" s="46"/>
@@ -31159,10 +31151,10 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="O20" s="84" t="s">
+      <c r="O20" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="P20" s="85"/>
+      <c r="P20" s="72"/>
     </row>
     <row r="21" spans="2:16" ht="30" customHeight="1">
       <c r="B21" s="5">
@@ -31194,10 +31186,10 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="O21" s="86" t="s">
+      <c r="O21" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="P21" s="87"/>
+      <c r="P21" s="74"/>
     </row>
     <row r="22" spans="2:16" ht="30" customHeight="1">
       <c r="B22" s="5">
@@ -31219,7 +31211,7 @@
         <v>46219</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" ref="H22:H23" si="2">IF(OR(F22="",G22=""),"",G22-F22+1)</f>
+        <f t="shared" ref="H22" si="2">IF(OR(F22="",G22=""),"",G22-F22+1)</f>
         <v>2</v>
       </c>
       <c r="I22" s="5">
@@ -31229,10 +31221,10 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
-      <c r="O22" s="88" t="s">
+      <c r="O22" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="P22" s="89"/>
+      <c r="P22" s="76"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
       <c r="B23" s="27"/>
@@ -31247,86 +31239,75 @@
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
-      <c r="O23" s="72" t="s">
+      <c r="O23" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="73"/>
+      <c r="P23" s="80"/>
     </row>
     <row r="24" spans="2:16" ht="15" customHeight="1">
-      <c r="O24" s="74" t="s">
+      <c r="O24" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="P24" s="75"/>
+      <c r="P24" s="82"/>
     </row>
     <row r="25" spans="2:16" ht="15" customHeight="1">
-      <c r="O25" s="76" t="s">
+      <c r="O25" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="P25" s="77"/>
+      <c r="P25" s="84"/>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1">
-      <c r="O26" s="78" t="s">
+      <c r="O26" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="79"/>
+      <c r="P26" s="86"/>
     </row>
     <row r="27" spans="2:16" ht="15" customHeight="1">
-      <c r="O27" s="80" t="s">
+      <c r="O27" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="81"/>
+      <c r="P27" s="88"/>
     </row>
     <row r="28" spans="2:16" ht="15" customHeight="1">
-      <c r="O28" s="70" t="s">
+      <c r="O28" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="P28" s="71"/>
+      <c r="P28" s="78"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="89"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="89"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="89"/>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="89"/>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="89"/>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="89"/>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -31335,34 +31316,45 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>AND(K$4&gt;=$F5,K$4&lt;=$G5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19:M19">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>AND(K$4&gt;=$F19,K$4&lt;=$G19)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K20:M20">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>AND(K$4&gt;=$F20,K$4&lt;=$G20)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:M22">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AND(K$4&gt;=$F22,K$4&lt;=$G22)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K21:M21">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND(K$4&gt;=$F21,K$4&lt;=$G21)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" sqref="C5:C22" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"기획,설계,개발,배포,테스트,문서화,발표준비"</formula1>
       <formula2>0</formula2>

--- a/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\팀 프로젝트\localhub\localhub\day03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vibecoding_team_pjt\day03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05A913A-FEE0-4411-8702-FAF4F12C67D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545BA2A-1129-48CC-AD3D-F65F8FE65C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="1425" windowWidth="18195" windowHeight="18690" tabRatio="500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="297">
   <si>
     <t>실습 소재</t>
   </si>
@@ -28035,6 +28035,12 @@
   <si>
     <t xml:space="preserve">완료 </t>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행중</t>
+  </si>
+  <si>
+    <t>예정</t>
   </si>
 </sst>
 </file>
@@ -28445,7 +28451,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -28542,6 +28548,12 @@
         <bgColor rgb="FF222222"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -28625,7 +28637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -28760,6 +28772,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -28769,13 +28787,7 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -28793,15 +28805,6 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -28817,29 +28820,17 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -28877,8 +28868,35 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -29520,7 +29538,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="52" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="48"/>
@@ -29529,7 +29547,7 @@
       <c r="F2" s="48"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="53" t="s">
         <v>140</v>
       </c>
       <c r="C3" s="46"/>
@@ -29564,16 +29582,16 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="54" t="s">
         <v>151</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="55" t="s">
         <v>154</v>
       </c>
       <c r="F6" s="28" t="s">
@@ -29581,19 +29599,19 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="55"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="55"/>
+      <c r="E8" s="51"/>
       <c r="F8" s="28" t="s">
         <v>156</v>
       </c>
@@ -29616,16 +29634,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="50" t="s">
         <v>161</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="55" t="s">
+      <c r="E10" s="51" t="s">
         <v>164</v>
       </c>
       <c r="F10" s="28" t="s">
@@ -29633,34 +29651,34 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
       <c r="D11" s="28"/>
-      <c r="E11" s="55"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="28"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
       <c r="D12" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="55"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="28" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="50" t="s">
         <v>167</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="51" t="s">
         <v>171</v>
       </c>
       <c r="F13" s="28" t="s">
@@ -29668,71 +29686,71 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
       <c r="D14" s="28"/>
-      <c r="E14" s="55"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
       <c r="D15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="E15" s="55"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="28" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="28"/>
-      <c r="E16" s="55"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="55"/>
+      <c r="E17" s="51"/>
       <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="50" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="55" t="s">
+      <c r="F18" s="51" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
       <c r="B21" s="29" t="s">
@@ -29752,16 +29770,16 @@
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="53" t="s">
+      <c r="B22" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="50" t="s">
         <v>184</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="55" t="s">
+      <c r="E22" s="51" t="s">
         <v>189</v>
       </c>
       <c r="F22" s="28" t="s">
@@ -29769,68 +29787,68 @@
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="55"/>
+      <c r="E23" s="51"/>
       <c r="F23" s="28"/>
     </row>
     <row r="24" spans="2:6" ht="30">
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
       <c r="D24" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="55"/>
+      <c r="E24" s="51"/>
       <c r="F24" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
       <c r="D25" s="28"/>
-      <c r="E25" s="55"/>
+      <c r="E25" s="51"/>
       <c r="F25" s="28"/>
     </row>
     <row r="26" spans="2:6" ht="30">
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
       <c r="D26" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="55"/>
+      <c r="E26" s="51"/>
       <c r="F26" s="28" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="55"/>
+      <c r="E27" s="51"/>
       <c r="F27" s="28"/>
     </row>
     <row r="28" spans="2:6" ht="30">
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="55"/>
+      <c r="E28" s="51"/>
       <c r="F28" s="28"/>
     </row>
     <row r="29" spans="2:6" ht="60">
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="50" t="s">
         <v>193</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="55" t="s">
+      <c r="E29" s="51" t="s">
         <v>197</v>
       </c>
       <c r="F29" s="28" t="s">
@@ -29838,50 +29856,50 @@
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="55"/>
+      <c r="E30" s="51"/>
       <c r="F30" s="28"/>
     </row>
     <row r="31" spans="2:6" ht="60">
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="55"/>
+      <c r="E31" s="51"/>
       <c r="F31" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
       <c r="D32" s="28"/>
-      <c r="E32" s="55"/>
+      <c r="E32" s="51"/>
       <c r="F32" s="28"/>
     </row>
     <row r="33" spans="2:6" ht="30">
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
       <c r="D33" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="55"/>
+      <c r="E33" s="51"/>
       <c r="F33" s="28"/>
     </row>
     <row r="34" spans="2:6" ht="30">
-      <c r="B34" s="53" t="s">
+      <c r="B34" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="53" t="s">
+      <c r="C34" s="50" t="s">
         <v>200</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E34" s="55" t="s">
+      <c r="E34" s="51" t="s">
         <v>203</v>
       </c>
       <c r="F34" s="28" t="s">
@@ -29889,34 +29907,34 @@
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="53"/>
-      <c r="C35" s="53"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="55"/>
+      <c r="E35" s="51"/>
       <c r="F35" s="28"/>
     </row>
     <row r="36" spans="2:6" ht="60">
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
       <c r="D36" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="55"/>
+      <c r="E36" s="51"/>
       <c r="F36" s="28" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="45">
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="53" t="s">
+      <c r="C37" s="50" t="s">
         <v>207</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="55" t="s">
+      <c r="E37" s="51" t="s">
         <v>210</v>
       </c>
       <c r="F37" s="28" t="s">
@@ -29924,19 +29942,19 @@
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
       <c r="D38" s="28"/>
-      <c r="E38" s="55"/>
+      <c r="E38" s="51"/>
       <c r="F38" s="28"/>
     </row>
     <row r="39" spans="2:6" ht="45">
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
       <c r="D39" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="55"/>
+      <c r="E39" s="51"/>
       <c r="F39" s="28" t="s">
         <v>212</v>
       </c>
@@ -30062,6 +30080,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="E22:E28"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="E37:E39"/>
@@ -30071,24 +30107,6 @@
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="E34:E36"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="B22:B28"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="E22:E28"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30402,13 +30420,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="52" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="48"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="68" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="39"/>
@@ -30446,10 +30464,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="62"/>
+      <c r="C9" s="67"/>
     </row>
     <row r="10" spans="2:3" ht="88.5" customHeight="1">
       <c r="B10" s="43" t="s">
@@ -30482,10 +30500,10 @@
       <c r="C14" s="44"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="67"/>
+      <c r="C16" s="64"/>
     </row>
     <row r="17" spans="2:3" ht="89.25" customHeight="1">
       <c r="B17" s="43" t="s">
@@ -30506,23 +30524,23 @@
       <c r="C19" s="44"/>
     </row>
     <row r="20" spans="2:3" ht="70.5" customHeight="1">
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="65" t="s">
         <v>263</v>
       </c>
       <c r="C20" s="44"/>
     </row>
     <row r="21" spans="2:3" ht="73.5" customHeight="1">
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="65" t="s">
         <v>264</v>
       </c>
       <c r="C21" s="44"/>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1"/>
     <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="61" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="62"/>
     </row>
     <row r="24" spans="2:3" ht="77.25" customHeight="1">
       <c r="B24" s="60" t="s">
@@ -30544,6 +30562,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B24:C24"/>
@@ -30556,12 +30580,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30591,7 +30609,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="83" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="48"/>
@@ -30607,7 +30625,7 @@
       <c r="M2" s="48"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="82" t="s">
         <v>135</v>
       </c>
       <c r="C3" s="46"/>
@@ -30689,7 +30707,7 @@
       <c r="J5" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="90"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
@@ -30722,7 +30740,7 @@
       <c r="J6" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="90"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -30750,10 +30768,12 @@
         <v>1</v>
       </c>
       <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="K7" s="90"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -30781,10 +30801,12 @@
         <v>1</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="K8" s="90"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
@@ -30812,12 +30834,12 @@
         <v>1</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="90"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
@@ -30835,21 +30857,23 @@
         <v>283</v>
       </c>
       <c r="F10" s="34">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="G10" s="34">
         <v>46218</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="K10" s="91"/>
+      <c r="L10" s="90"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="2:13" ht="30" customHeight="1">
@@ -30866,23 +30890,23 @@
         <v>284</v>
       </c>
       <c r="F11" s="34">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="G11" s="34">
         <v>46218</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="90"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:13" ht="30" customHeight="1">
@@ -30899,22 +30923,24 @@
         <v>285</v>
       </c>
       <c r="F12" s="34">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="G12" s="34">
         <v>46218</v>
       </c>
       <c r="H12" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="5">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+        <v>100</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="K12" s="91"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="91"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
       <c r="B13" s="5">
@@ -30940,11 +30966,13 @@
         <v>1</v>
       </c>
       <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="L13" s="90"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="2:13" ht="30" customHeight="1">
@@ -30971,13 +30999,13 @@
         <v>1</v>
       </c>
       <c r="I14" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>293</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="90"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:13" ht="30" customHeight="1">
@@ -30997,19 +31025,21 @@
         <v>46218</v>
       </c>
       <c r="G15" s="34">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="5">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="L15" s="90"/>
+      <c r="M15" s="90"/>
     </row>
     <row r="16" spans="2:13" ht="30" customHeight="1">
       <c r="B16" s="5">
@@ -31025,22 +31055,24 @@
         <v>285</v>
       </c>
       <c r="F16" s="34">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="G16" s="34">
         <v>46219</v>
       </c>
       <c r="H16" s="5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="L16" s="91"/>
+      <c r="M16" s="90"/>
     </row>
     <row r="17" spans="2:16" ht="30" customHeight="1">
       <c r="B17" s="5">
@@ -31056,10 +31088,10 @@
         <v>284</v>
       </c>
       <c r="F17" s="34">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="G17" s="34">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="H17" s="5">
         <f t="shared" si="0"/>
@@ -31068,10 +31100,12 @@
       <c r="I17" s="5">
         <v>0</v>
       </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="3"/>
+      <c r="J17" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="K17" s="91"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="M17" s="90"/>
     </row>
     <row r="18" spans="2:16" ht="30" customHeight="1">
       <c r="B18" s="5">
@@ -31099,10 +31133,12 @@
       <c r="I18" s="5">
         <v>0</v>
       </c>
-      <c r="J18" s="5"/>
+      <c r="J18" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="M18" s="90"/>
     </row>
     <row r="19" spans="2:16" ht="30" customHeight="1">
       <c r="B19" s="5">
@@ -31130,10 +31166,12 @@
       <c r="I19" s="5">
         <v>0</v>
       </c>
-      <c r="J19" s="5"/>
+      <c r="J19" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="M19" s="90"/>
     </row>
     <row r="20" spans="2:16" ht="30" customHeight="1">
       <c r="B20" s="5">
@@ -31149,26 +31187,28 @@
         <v>283</v>
       </c>
       <c r="F20" s="34">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="G20" s="34">
         <v>46219</v>
       </c>
       <c r="H20" s="5">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
       </c>
-      <c r="J20" s="5"/>
+      <c r="J20" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="O20" s="71" t="s">
+      <c r="L20" s="91"/>
+      <c r="M20" s="90"/>
+      <c r="O20" s="84" t="s">
         <v>136</v>
       </c>
-      <c r="P20" s="72"/>
+      <c r="P20" s="85"/>
     </row>
     <row r="21" spans="2:16" ht="30" customHeight="1">
       <c r="B21" s="5">
@@ -31194,16 +31234,18 @@
         <v>1</v>
       </c>
       <c r="I21" s="5">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="O21" s="73" t="s">
+      <c r="M21" s="90"/>
+      <c r="O21" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="P21" s="74"/>
+      <c r="P21" s="87"/>
     </row>
     <row r="22" spans="2:16" ht="30" customHeight="1">
       <c r="B22" s="5">
@@ -31219,26 +31261,28 @@
         <v>271</v>
       </c>
       <c r="F22" s="34">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="G22" s="34">
         <v>46219</v>
       </c>
       <c r="H22" s="5">
         <f t="shared" ref="H22" si="2">IF(OR(F22="",G22=""),"",G22-F22+1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
-      <c r="J22" s="5"/>
+      <c r="J22" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="O22" s="75" t="s">
+      <c r="L22" s="91"/>
+      <c r="M22" s="90"/>
+      <c r="O22" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="P22" s="76"/>
+      <c r="P22" s="89"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
       <c r="B23" s="27"/>
@@ -31253,75 +31297,86 @@
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
-      <c r="O23" s="79" t="s">
+      <c r="O23" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="80"/>
+      <c r="P23" s="73"/>
     </row>
     <row r="24" spans="2:16" ht="15" customHeight="1">
-      <c r="O24" s="81" t="s">
+      <c r="O24" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="P24" s="82"/>
+      <c r="P24" s="75"/>
     </row>
     <row r="25" spans="2:16" ht="15" customHeight="1">
-      <c r="O25" s="83" t="s">
+      <c r="O25" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="P25" s="84"/>
+      <c r="P25" s="77"/>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1">
-      <c r="O26" s="85" t="s">
+      <c r="O26" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="86"/>
+      <c r="P26" s="79"/>
     </row>
     <row r="27" spans="2:16" ht="15" customHeight="1">
-      <c r="O27" s="87" t="s">
+      <c r="O27" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="88"/>
+      <c r="P27" s="81"/>
     </row>
     <row r="28" spans="2:16" ht="15" customHeight="1">
-      <c r="O28" s="77" t="s">
+      <c r="O28" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="P28" s="78"/>
+      <c r="P28" s="71"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="89"/>
-      <c r="C33" s="89"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="89"/>
-      <c r="C35" s="89"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="89"/>
-      <c r="C36" s="89"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -31330,17 +31385,6 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">

--- a/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vibecoding_team_pjt\day03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545BA2A-1129-48CC-AD3D-F65F8FE65C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D2189E-C4AB-4D58-A21F-445B8C7EA2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -28738,6 +28738,12 @@
     <xf numFmtId="177" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -28772,12 +28778,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -28787,7 +28787,13 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -28805,6 +28811,15 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -28820,17 +28835,29 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -28868,35 +28895,8 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -29221,10 +29221,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="44"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
       <c r="B4" s="13" t="s">
@@ -29259,10 +29259,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="39"/>
+      <c r="C9" s="41"/>
     </row>
     <row r="10" spans="2:3" ht="27">
       <c r="B10" s="4" t="s">
@@ -29313,28 +29313,28 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="41"/>
+      <c r="C17" s="43"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="44"/>
+      <c r="C18" s="46"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="37"/>
+      <c r="C19" s="39"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="39"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -29368,13 +29368,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
       <c r="B4" s="6" t="s">
@@ -29466,46 +29466,46 @@
     </row>
     <row r="9" spans="2:10" ht="14.1" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="39"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="41"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
       <c r="B12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
       <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -29541,19 +29541,19 @@
       <c r="B2" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
       <c r="B3" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="39"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="2:6" ht="35.65" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -29591,7 +29591,7 @@
       <c r="D6" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="56" t="s">
         <v>154</v>
       </c>
       <c r="F6" s="28" t="s">
@@ -29599,19 +29599,19 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="51"/>
+      <c r="E7" s="57"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
       <c r="D8" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="51"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="28" t="s">
         <v>156</v>
       </c>
@@ -29634,16 +29634,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="55" t="s">
         <v>161</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="57" t="s">
         <v>164</v>
       </c>
       <c r="F10" s="28" t="s">
@@ -29651,34 +29651,34 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
       <c r="D11" s="28"/>
-      <c r="E11" s="51"/>
+      <c r="E11" s="57"/>
       <c r="F11" s="28"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
       <c r="D12" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="51"/>
+      <c r="E12" s="57"/>
       <c r="F12" s="28" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="50" t="s">
+      <c r="B13" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="55" t="s">
         <v>167</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="57" t="s">
         <v>171</v>
       </c>
       <c r="F13" s="28" t="s">
@@ -29686,71 +29686,71 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="28"/>
-      <c r="E14" s="51"/>
+      <c r="E14" s="57"/>
       <c r="F14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
       <c r="D15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="E15" s="51"/>
+      <c r="E15" s="57"/>
       <c r="F15" s="28" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
       <c r="D16" s="28"/>
-      <c r="E16" s="51"/>
+      <c r="E16" s="57"/>
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="51"/>
+      <c r="E17" s="57"/>
       <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="55" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="57" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
       <c r="D20" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
       <c r="B21" s="29" t="s">
@@ -29770,16 +29770,16 @@
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="55" t="s">
         <v>184</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="57" t="s">
         <v>189</v>
       </c>
       <c r="F22" s="28" t="s">
@@ -29787,68 +29787,68 @@
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="51"/>
+      <c r="E23" s="57"/>
       <c r="F23" s="28"/>
     </row>
     <row r="24" spans="2:6" ht="30">
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
       <c r="D24" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="51"/>
+      <c r="E24" s="57"/>
       <c r="F24" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
       <c r="D25" s="28"/>
-      <c r="E25" s="51"/>
+      <c r="E25" s="57"/>
       <c r="F25" s="28"/>
     </row>
     <row r="26" spans="2:6" ht="30">
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
       <c r="D26" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="51"/>
+      <c r="E26" s="57"/>
       <c r="F26" s="28" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="51"/>
+      <c r="E27" s="57"/>
       <c r="F27" s="28"/>
     </row>
     <row r="28" spans="2:6" ht="30">
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
       <c r="D28" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="51"/>
+      <c r="E28" s="57"/>
       <c r="F28" s="28"/>
     </row>
     <row r="29" spans="2:6" ht="60">
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="55" t="s">
         <v>193</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="57" t="s">
         <v>197</v>
       </c>
       <c r="F29" s="28" t="s">
@@ -29856,50 +29856,50 @@
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="51"/>
+      <c r="E30" s="57"/>
       <c r="F30" s="28"/>
     </row>
     <row r="31" spans="2:6" ht="60">
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="55"/>
       <c r="D31" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="51"/>
+      <c r="E31" s="57"/>
       <c r="F31" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
       <c r="D32" s="28"/>
-      <c r="E32" s="51"/>
+      <c r="E32" s="57"/>
       <c r="F32" s="28"/>
     </row>
     <row r="33" spans="2:6" ht="30">
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
       <c r="D33" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="51"/>
+      <c r="E33" s="57"/>
       <c r="F33" s="28"/>
     </row>
     <row r="34" spans="2:6" ht="30">
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="55" t="s">
         <v>200</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="57" t="s">
         <v>203</v>
       </c>
       <c r="F34" s="28" t="s">
@@ -29907,34 +29907,34 @@
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="51"/>
+      <c r="E35" s="57"/>
       <c r="F35" s="28"/>
     </row>
     <row r="36" spans="2:6" ht="60">
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
       <c r="D36" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="51"/>
+      <c r="E36" s="57"/>
       <c r="F36" s="28" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="45">
-      <c r="B37" s="50" t="s">
+      <c r="B37" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="55" t="s">
         <v>207</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="51" t="s">
+      <c r="E37" s="57" t="s">
         <v>210</v>
       </c>
       <c r="F37" s="28" t="s">
@@ -29942,19 +29942,19 @@
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
       <c r="D38" s="28"/>
-      <c r="E38" s="51"/>
+      <c r="E38" s="57"/>
       <c r="F38" s="28"/>
     </row>
     <row r="39" spans="2:6" ht="45">
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
       <c r="D39" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="51"/>
+      <c r="E39" s="57"/>
       <c r="F39" s="28" t="s">
         <v>212</v>
       </c>
@@ -30080,24 +30080,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="B22:B28"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="E22:E28"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="E37:E39"/>
@@ -30107,6 +30089,24 @@
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="E34:E36"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="E22:E28"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30131,37 +30131,37 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
     </row>
     <row r="3" spans="2:8" ht="72.400000000000006" customHeight="1">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="39"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="39"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
       <c r="B5" s="10" t="s">
@@ -30368,14 +30368,14 @@
       <c r="B15" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="60" t="s">
         <v>265</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="41"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -30423,13 +30423,13 @@
       <c r="B2" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="48"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="39"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -30464,110 +30464,104 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="67"/>
+      <c r="C9" s="64"/>
     </row>
     <row r="10" spans="2:3" ht="88.5" customHeight="1">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="46"/>
     </row>
     <row r="11" spans="2:3" ht="73.5" customHeight="1">
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="62" t="s">
         <v>253</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="46"/>
     </row>
     <row r="12" spans="2:3" ht="118.5" customHeight="1">
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="62" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="44"/>
+      <c r="C12" s="46"/>
     </row>
     <row r="13" spans="2:3" ht="116.25" customHeight="1">
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="44"/>
+      <c r="C13" s="46"/>
     </row>
     <row r="14" spans="2:3" ht="63" customHeight="1">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="45" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="44"/>
+      <c r="C14" s="46"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="64"/>
+      <c r="C16" s="69"/>
     </row>
     <row r="17" spans="2:3" ht="89.25" customHeight="1">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="C17" s="44"/>
+      <c r="C17" s="46"/>
     </row>
     <row r="18" spans="2:3" ht="85.5" customHeight="1">
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="62" t="s">
         <v>258</v>
       </c>
-      <c r="C18" s="44"/>
+      <c r="C18" s="46"/>
     </row>
     <row r="19" spans="2:3" ht="99.75" customHeight="1">
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="62" t="s">
         <v>259</v>
       </c>
-      <c r="C19" s="44"/>
+      <c r="C19" s="46"/>
     </row>
     <row r="20" spans="2:3" ht="70.5" customHeight="1">
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="70" t="s">
         <v>263</v>
       </c>
-      <c r="C20" s="44"/>
+      <c r="C20" s="46"/>
     </row>
     <row r="21" spans="2:3" ht="73.5" customHeight="1">
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="70" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="44"/>
+      <c r="C21" s="46"/>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1"/>
     <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="62"/>
+      <c r="C23" s="67"/>
     </row>
     <row r="24" spans="2:3" ht="77.25" customHeight="1">
-      <c r="B24" s="60" t="s">
+      <c r="B24" s="62" t="s">
         <v>260</v>
       </c>
-      <c r="C24" s="44"/>
+      <c r="C24" s="46"/>
     </row>
     <row r="25" spans="2:3" ht="55.5" customHeight="1">
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="45" t="s">
         <v>261</v>
       </c>
-      <c r="C25" s="44"/>
+      <c r="C25" s="46"/>
     </row>
     <row r="26" spans="2:3" ht="56.25" customHeight="1">
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="62" t="s">
         <v>262</v>
       </c>
-      <c r="C26" s="44"/>
+      <c r="C26" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B24:C24"/>
@@ -30580,6 +30574,12 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30609,36 +30609,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="39"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="41"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
       <c r="B4" s="12" t="s">
@@ -30707,7 +30707,7 @@
       <c r="J5" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K5" s="90"/>
+      <c r="K5" s="36"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
@@ -30740,7 +30740,7 @@
       <c r="J6" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K6" s="90"/>
+      <c r="K6" s="36"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
@@ -30773,7 +30773,7 @@
       <c r="J7" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K7" s="90"/>
+      <c r="K7" s="36"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
@@ -30806,7 +30806,7 @@
       <c r="J8" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K8" s="90"/>
+      <c r="K8" s="36"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
@@ -30839,7 +30839,7 @@
       <c r="J9" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="K9" s="90"/>
+      <c r="K9" s="36"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
@@ -30872,8 +30872,8 @@
       <c r="J10" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K10" s="91"/>
-      <c r="L10" s="90"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="36"/>
       <c r="M10" s="3"/>
     </row>
     <row r="11" spans="2:13" ht="30" customHeight="1">
@@ -30905,8 +30905,8 @@
       <c r="J11" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="K11" s="91"/>
-      <c r="L11" s="90"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="36"/>
       <c r="M11" s="3"/>
     </row>
     <row r="12" spans="2:13" ht="30" customHeight="1">
@@ -30938,9 +30938,9 @@
       <c r="J12" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="K12" s="91"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="91"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="37"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
       <c r="B13" s="5">
@@ -30969,10 +30969,10 @@
         <v>100</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K13" s="3"/>
-      <c r="L13" s="90"/>
+      <c r="L13" s="36"/>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="2:13" ht="30" customHeight="1">
@@ -31005,7 +31005,7 @@
         <v>293</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="90"/>
+      <c r="L14" s="36"/>
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="2:13" ht="30" customHeight="1">
@@ -31032,14 +31032,14 @@
         <v>2</v>
       </c>
       <c r="I15" s="5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>295</v>
       </c>
       <c r="K15" s="3"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
     </row>
     <row r="16" spans="2:13" ht="30" customHeight="1">
       <c r="B16" s="5">
@@ -31071,8 +31071,8 @@
         <v>296</v>
       </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="91"/>
-      <c r="M16" s="90"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="36"/>
     </row>
     <row r="17" spans="2:16" ht="30" customHeight="1">
       <c r="B17" s="5">
@@ -31098,14 +31098,14 @@
         <v>1</v>
       </c>
       <c r="I17" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="K17" s="91"/>
+        <v>292</v>
+      </c>
+      <c r="K17" s="37"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="90"/>
+      <c r="M17" s="36"/>
     </row>
     <row r="18" spans="2:16" ht="30" customHeight="1">
       <c r="B18" s="5">
@@ -31131,14 +31131,14 @@
         <v>1</v>
       </c>
       <c r="I18" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
-      <c r="M18" s="90"/>
+      <c r="M18" s="36"/>
     </row>
     <row r="19" spans="2:16" ht="30" customHeight="1">
       <c r="B19" s="5">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-      <c r="M19" s="90"/>
+      <c r="M19" s="36"/>
     </row>
     <row r="20" spans="2:16" ht="30" customHeight="1">
       <c r="B20" s="5">
@@ -31203,12 +31203,12 @@
         <v>296</v>
       </c>
       <c r="K20" s="3"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="90"/>
-      <c r="O20" s="84" t="s">
+      <c r="L20" s="37"/>
+      <c r="M20" s="36"/>
+      <c r="O20" s="73" t="s">
         <v>136</v>
       </c>
-      <c r="P20" s="85"/>
+      <c r="P20" s="74"/>
     </row>
     <row r="21" spans="2:16" ht="30" customHeight="1">
       <c r="B21" s="5">
@@ -31234,18 +31234,18 @@
         <v>1</v>
       </c>
       <c r="I21" s="5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
-      <c r="M21" s="90"/>
-      <c r="O21" s="86" t="s">
+      <c r="M21" s="36"/>
+      <c r="O21" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="P21" s="87"/>
+      <c r="P21" s="76"/>
     </row>
     <row r="22" spans="2:16" ht="30" customHeight="1">
       <c r="B22" s="5">
@@ -31277,12 +31277,12 @@
         <v>296</v>
       </c>
       <c r="K22" s="3"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="90"/>
-      <c r="O22" s="88" t="s">
+      <c r="L22" s="37"/>
+      <c r="M22" s="36"/>
+      <c r="O22" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="P22" s="89"/>
+      <c r="P22" s="78"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
       <c r="B23" s="27"/>
@@ -31297,86 +31297,75 @@
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
-      <c r="O23" s="72" t="s">
+      <c r="O23" s="81" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="73"/>
+      <c r="P23" s="82"/>
     </row>
     <row r="24" spans="2:16" ht="15" customHeight="1">
-      <c r="O24" s="74" t="s">
+      <c r="O24" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="P24" s="75"/>
+      <c r="P24" s="84"/>
     </row>
     <row r="25" spans="2:16" ht="15" customHeight="1">
-      <c r="O25" s="76" t="s">
+      <c r="O25" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="P25" s="77"/>
+      <c r="P25" s="86"/>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1">
-      <c r="O26" s="78" t="s">
+      <c r="O26" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="79"/>
+      <c r="P26" s="88"/>
     </row>
     <row r="27" spans="2:16" ht="15" customHeight="1">
-      <c r="O27" s="80" t="s">
+      <c r="O27" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="81"/>
+      <c r="P27" s="90"/>
     </row>
     <row r="28" spans="2:16" ht="15" customHeight="1">
-      <c r="O28" s="70" t="s">
+      <c r="O28" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="P28" s="71"/>
+      <c r="P28" s="80"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
+      <c r="B30" s="91"/>
+      <c r="C30" s="91"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
+      <c r="B32" s="91"/>
+      <c r="C32" s="91"/>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
+      <c r="B34" s="91"/>
+      <c r="C34" s="91"/>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
+      <c r="B35" s="91"/>
+      <c r="C35" s="91"/>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
+      <c r="B36" s="91"/>
+      <c r="C36" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -31385,6 +31374,17 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
@@ -31441,16 +31441,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="48"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="39"/>
+      <c r="C3" s="41"/>
     </row>
     <row r="5" spans="2:3" ht="19.5" customHeight="1">
       <c r="B5" s="6" t="s">

--- a/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
+++ b/day03/04_3일차_팀프로젝트_실습기획서_템플렛.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vibecoding_team_pjt\day03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D2189E-C4AB-4D58-A21F-445B8C7EA2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB027AA-7301-4F1E-B4A7-02983BA7A26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3240" yWindow="3240" windowWidth="28800" windowHeight="15345" tabRatio="500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="296">
   <si>
     <t>실습 소재</t>
   </si>
@@ -28035,9 +28035,6 @@
   <si>
     <t xml:space="preserve">완료 </t>
     <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행중</t>
   </si>
   <si>
     <t>예정</t>
@@ -28778,6 +28775,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -28787,13 +28790,7 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -28811,15 +28808,6 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -28835,29 +28823,17 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -28895,8 +28871,29 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -29538,7 +29535,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="54" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="50"/>
@@ -29547,7 +29544,7 @@
       <c r="F2" s="50"/>
     </row>
     <row r="3" spans="2:6" ht="28.35" customHeight="1">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="55" t="s">
         <v>140</v>
       </c>
       <c r="C3" s="48"/>
@@ -29582,16 +29579,16 @@
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="2:6" ht="30" customHeight="1">
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="56" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="56" t="s">
         <v>151</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="57" t="s">
         <v>154</v>
       </c>
       <c r="F6" s="28" t="s">
@@ -29599,19 +29596,19 @@
       </c>
     </row>
     <row r="7" spans="2:6" ht="30" customHeight="1">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
       <c r="D7" s="28"/>
-      <c r="E7" s="57"/>
+      <c r="E7" s="53"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="2:6" ht="30" customHeight="1">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
       <c r="D8" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="57"/>
+      <c r="E8" s="53"/>
       <c r="F8" s="28" t="s">
         <v>156</v>
       </c>
@@ -29634,16 +29631,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="30" customHeight="1">
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="52" t="s">
         <v>161</v>
       </c>
       <c r="D10" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="53" t="s">
         <v>164</v>
       </c>
       <c r="F10" s="28" t="s">
@@ -29651,34 +29648,34 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="30" customHeight="1">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="28"/>
-      <c r="E11" s="57"/>
+      <c r="E11" s="53"/>
       <c r="F11" s="28"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
       <c r="D12" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="57"/>
+      <c r="E12" s="53"/>
       <c r="F12" s="28" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="52" t="s">
         <v>167</v>
       </c>
       <c r="D13" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="53" t="s">
         <v>171</v>
       </c>
       <c r="F13" s="28" t="s">
@@ -29686,71 +29683,71 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="30" customHeight="1">
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="28"/>
-      <c r="E14" s="57"/>
+      <c r="E14" s="53"/>
       <c r="F14" s="28"/>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
       <c r="D15" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="E15" s="57"/>
+      <c r="E15" s="53"/>
       <c r="F15" s="28" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="28"/>
-      <c r="E16" s="57"/>
+      <c r="E16" s="53"/>
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="57"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="28"/>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="52" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="57" t="s">
+      <c r="E18" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="57" t="s">
+      <c r="F18" s="53" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="28"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
       <c r="B21" s="29" t="s">
@@ -29770,16 +29767,16 @@
       </c>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="52" t="s">
         <v>184</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="53" t="s">
         <v>189</v>
       </c>
       <c r="F22" s="28" t="s">
@@ -29787,68 +29784,68 @@
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="28"/>
-      <c r="E23" s="57"/>
+      <c r="E23" s="53"/>
       <c r="F23" s="28"/>
     </row>
     <row r="24" spans="2:6" ht="30">
-      <c r="B24" s="55"/>
-      <c r="C24" s="55"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="57"/>
+      <c r="E24" s="53"/>
       <c r="F24" s="28" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="55"/>
-      <c r="C25" s="55"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="28"/>
-      <c r="E25" s="57"/>
+      <c r="E25" s="53"/>
       <c r="F25" s="28"/>
     </row>
     <row r="26" spans="2:6" ht="30">
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="57"/>
+      <c r="E26" s="53"/>
       <c r="F26" s="28" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="28"/>
-      <c r="E27" s="57"/>
+      <c r="E27" s="53"/>
       <c r="F27" s="28"/>
     </row>
     <row r="28" spans="2:6" ht="30">
-      <c r="B28" s="55"/>
-      <c r="C28" s="55"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="E28" s="57"/>
+      <c r="E28" s="53"/>
       <c r="F28" s="28"/>
     </row>
     <row r="29" spans="2:6" ht="60">
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="52" t="s">
         <v>193</v>
       </c>
       <c r="D29" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="53" t="s">
         <v>197</v>
       </c>
       <c r="F29" s="28" t="s">
@@ -29856,50 +29853,50 @@
       </c>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
       <c r="D30" s="28"/>
-      <c r="E30" s="57"/>
+      <c r="E30" s="53"/>
       <c r="F30" s="28"/>
     </row>
     <row r="31" spans="2:6" ht="60">
-      <c r="B31" s="55"/>
-      <c r="C31" s="55"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
       <c r="D31" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="57"/>
+      <c r="E31" s="53"/>
       <c r="F31" s="28" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
       <c r="D32" s="28"/>
-      <c r="E32" s="57"/>
+      <c r="E32" s="53"/>
       <c r="F32" s="28"/>
     </row>
     <row r="33" spans="2:6" ht="30">
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
       <c r="D33" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="57"/>
+      <c r="E33" s="53"/>
       <c r="F33" s="28"/>
     </row>
     <row r="34" spans="2:6" ht="30">
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="C34" s="52" t="s">
         <v>200</v>
       </c>
       <c r="D34" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="E34" s="57" t="s">
+      <c r="E34" s="53" t="s">
         <v>203</v>
       </c>
       <c r="F34" s="28" t="s">
@@ -29907,34 +29904,34 @@
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
       <c r="D35" s="28"/>
-      <c r="E35" s="57"/>
+      <c r="E35" s="53"/>
       <c r="F35" s="28"/>
     </row>
     <row r="36" spans="2:6" ht="60">
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
       <c r="D36" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="57"/>
+      <c r="E36" s="53"/>
       <c r="F36" s="28" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="45">
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="55" t="s">
+      <c r="C37" s="52" t="s">
         <v>207</v>
       </c>
       <c r="D37" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="53" t="s">
         <v>210</v>
       </c>
       <c r="F37" s="28" t="s">
@@ -29942,19 +29939,19 @@
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
       <c r="D38" s="28"/>
-      <c r="E38" s="57"/>
+      <c r="E38" s="53"/>
       <c r="F38" s="28"/>
     </row>
     <row r="39" spans="2:6" ht="45">
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
       <c r="D39" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="57"/>
+      <c r="E39" s="53"/>
       <c r="F39" s="28" t="s">
         <v>212</v>
       </c>
@@ -30080,6 +30077,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="C22:C28"/>
+    <mergeCell ref="E22:E28"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:C39"/>
     <mergeCell ref="E37:E39"/>
@@ -30089,24 +30104,6 @@
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C34:C36"/>
     <mergeCell ref="E34:E36"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="B22:B28"/>
-    <mergeCell ref="C22:C28"/>
-    <mergeCell ref="E22:E28"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30420,13 +30417,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="54" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="50"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="70" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="41"/>
@@ -30464,10 +30461,10 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="64"/>
+      <c r="C9" s="69"/>
     </row>
     <row r="10" spans="2:3" ht="88.5" customHeight="1">
       <c r="B10" s="45" t="s">
@@ -30500,10 +30497,10 @@
       <c r="C14" s="46"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="69"/>
+      <c r="C16" s="66"/>
     </row>
     <row r="17" spans="2:3" ht="89.25" customHeight="1">
       <c r="B17" s="45" t="s">
@@ -30524,23 +30521,23 @@
       <c r="C19" s="46"/>
     </row>
     <row r="20" spans="2:3" ht="70.5" customHeight="1">
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="67" t="s">
         <v>263</v>
       </c>
       <c r="C20" s="46"/>
     </row>
     <row r="21" spans="2:3" ht="73.5" customHeight="1">
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="67" t="s">
         <v>264</v>
       </c>
       <c r="C21" s="46"/>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1"/>
     <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="67"/>
+      <c r="C23" s="64"/>
     </row>
     <row r="24" spans="2:3" ht="77.25" customHeight="1">
       <c r="B24" s="62" t="s">
@@ -30562,6 +30559,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B24:C24"/>
@@ -30574,12 +30577,6 @@
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30609,7 +30606,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="85" t="s">
         <v>51</v>
       </c>
       <c r="C2" s="50"/>
@@ -30625,7 +30622,7 @@
       <c r="M2" s="50"/>
     </row>
     <row r="3" spans="2:13" ht="79.7" customHeight="1">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="84" t="s">
         <v>135</v>
       </c>
       <c r="C3" s="48"/>
@@ -31032,10 +31029,10 @@
         <v>2</v>
       </c>
       <c r="I15" s="5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="36"/>
@@ -31068,7 +31065,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="37"/>
@@ -31164,10 +31161,10 @@
         <v>1</v>
       </c>
       <c r="I19" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
@@ -31197,18 +31194,18 @@
         <v>1</v>
       </c>
       <c r="I20" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="37"/>
       <c r="M20" s="36"/>
-      <c r="O20" s="73" t="s">
+      <c r="O20" s="86" t="s">
         <v>136</v>
       </c>
-      <c r="P20" s="74"/>
+      <c r="P20" s="87"/>
     </row>
     <row r="21" spans="2:16" ht="30" customHeight="1">
       <c r="B21" s="5">
@@ -31242,10 +31239,10 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="36"/>
-      <c r="O21" s="75" t="s">
+      <c r="O21" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="P21" s="76"/>
+      <c r="P21" s="89"/>
     </row>
     <row r="22" spans="2:16" ht="30" customHeight="1">
       <c r="B22" s="5">
@@ -31271,18 +31268,18 @@
         <v>1</v>
       </c>
       <c r="I22" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="37"/>
       <c r="M22" s="36"/>
-      <c r="O22" s="77" t="s">
+      <c r="O22" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="P22" s="78"/>
+      <c r="P22" s="91"/>
     </row>
     <row r="23" spans="2:16" ht="30" customHeight="1">
       <c r="B23" s="27"/>
@@ -31297,75 +31294,86 @@
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
-      <c r="O23" s="81" t="s">
+      <c r="O23" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="82"/>
+      <c r="P23" s="75"/>
     </row>
     <row r="24" spans="2:16" ht="15" customHeight="1">
-      <c r="O24" s="83" t="s">
+      <c r="O24" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="P24" s="84"/>
+      <c r="P24" s="77"/>
     </row>
     <row r="25" spans="2:16" ht="15" customHeight="1">
-      <c r="O25" s="85" t="s">
+      <c r="O25" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="P25" s="86"/>
+      <c r="P25" s="79"/>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1">
-      <c r="O26" s="87" t="s">
+      <c r="O26" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="P26" s="88"/>
+      <c r="P26" s="81"/>
     </row>
     <row r="27" spans="2:16" ht="15" customHeight="1">
-      <c r="O27" s="89" t="s">
+      <c r="O27" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="P27" s="90"/>
+      <c r="P27" s="83"/>
     </row>
     <row r="28" spans="2:16" ht="15" customHeight="1">
-      <c r="O28" s="79" t="s">
+      <c r="O28" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="P28" s="80"/>
+      <c r="P28" s="73"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="91"/>
-      <c r="C29" s="91"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
     </row>
     <row r="30" spans="2:16">
-      <c r="B30" s="91"/>
-      <c r="C30" s="91"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="71"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="91"/>
-      <c r="C32" s="91"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="91"/>
-      <c r="C33" s="91"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="71"/>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="91"/>
-      <c r="C34" s="91"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="91"/>
-      <c r="C35" s="91"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="91"/>
-      <c r="C36" s="91"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -31374,17 +31382,6 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="O22:P22"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
